--- a/informes/informe_seguimiento_dennis.xlsx
+++ b/informes/informe_seguimiento_dennis.xlsx
@@ -162,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -207,6 +207,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1623,7 +1626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1639,199 +1642,297 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1">
+    <row r="3" ht="20" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
+          <t>Proactividad comercial</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
           <t>Métrica</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>Mar 2026</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>Abr 2026</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D4" s="18" t="inlineStr">
         <is>
           <t>Objetivo</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>Desgaste total</t>
         </is>
       </c>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C4" s="20" t="n">
+      <c r="C5" s="21" t="n">
         <v>267.68</v>
       </c>
-      <c r="D4" s="21" t="inlineStr">
+      <c r="D5" s="22" t="inlineStr">
         <is>
           <t>200 pts</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="22" t="inlineStr">
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>Posición ranking</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C5" s="24" t="n">
+      <c r="C6" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>Full/Long Drive</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>11,1 ops</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>Calidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Abr 2026</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>Objetivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>CAL1SEM</t>
         </is>
       </c>
-      <c r="B6" s="20" t="n">
+      <c r="B11" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="25" t="n">
+      <c r="C11" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>5,0</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="22" t="inlineStr">
-        <is>
-          <t>Full/Long Drive</t>
-        </is>
-      </c>
-      <c r="B7" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>11,1 ops</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Horch Lauden</t>
         </is>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>Abr 2026</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>Objetivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>Horch Lauden</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C15" s="21" t="n">
         <v>158</v>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>≤50</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="22" t="inlineStr">
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>ONE KVPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>Abr 2026</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>Objetivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>Score ONE</t>
         </is>
       </c>
-      <c r="B9" s="24" t="n">
+      <c r="B19" s="21" t="n">
         <v>6.1</v>
       </c>
-      <c r="C9" s="26" t="n">
+      <c r="C19" s="27" t="n">
         <v>5.3</v>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>6,2</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="23" t="inlineStr">
         <is>
           <t>Service CAM (%)</t>
         </is>
       </c>
-      <c r="B10" s="20" t="n">
+      <c r="B20" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C20" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="22" t="inlineStr">
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>Diferidos (%)</t>
         </is>
       </c>
-      <c r="B11" s="24" t="n">
+      <c r="B21" s="21" t="n">
         <v>32</v>
       </c>
-      <c r="C11" s="26" t="n">
+      <c r="C21" s="27" t="n">
         <v>30</v>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="23" t="inlineStr">
         <is>
           <t>Multimedia</t>
         </is>
       </c>
-      <c r="B12" s="20" t="n">
+      <c r="B22" s="25" t="n">
         <v>7.4</v>
       </c>
-      <c r="C12" s="26" t="n">
+      <c r="C22" s="27" t="n">
         <v>6.8</v>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="5">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1860,29 +1961,29 @@
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>Métrica</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>Referencia</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="17" t="inlineStr">
         <is>
           <t>Positivo si...</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="D3" s="17" t="inlineStr">
         <is>
           <t>Mejorar si...</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="27" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>Desgaste total</t>
         </is>
@@ -1892,19 +1993,19 @@
           <t>&gt;200 pts</t>
         </is>
       </c>
-      <c r="C4" s="28" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t>≥200 pts</t>
         </is>
       </c>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="D4" s="30" t="inlineStr">
         <is>
           <t>&lt;200 pts — seguimiento prioritario</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="30" t="inlineStr">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t>CAL1SEM</t>
         </is>
@@ -1914,19 +2015,19 @@
           <t>≥5,0</t>
         </is>
       </c>
-      <c r="C5" s="28" t="inlineStr">
+      <c r="C5" s="29" t="inlineStr">
         <is>
           <t>≥5,0</t>
         </is>
       </c>
-      <c r="D5" s="29" t="inlineStr">
+      <c r="D5" s="30" t="inlineStr">
         <is>
           <t>&lt;5,0</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="27" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>Full/Long Drive</t>
         </is>
@@ -1936,19 +2037,19 @@
           <t>Media equipo: 11,1 ops</t>
         </is>
       </c>
-      <c r="C6" s="28" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>&gt;11,1 ops</t>
         </is>
       </c>
-      <c r="D6" s="29" t="inlineStr">
+      <c r="D6" s="30" t="inlineStr">
         <is>
           <t>≤11,1 ops</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="30" t="inlineStr">
+      <c r="A7" s="31" t="inlineStr">
         <is>
           <t>Fidelidad</t>
         </is>
@@ -1958,19 +2059,19 @@
           <t>Media equipo: 63,48%</t>
         </is>
       </c>
-      <c r="C7" s="28" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>≥63,48%</t>
         </is>
       </c>
-      <c r="D7" s="29" t="inlineStr">
+      <c r="D7" s="30" t="inlineStr">
         <is>
           <t>&lt;63,48%</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>Horch Lauden (pos)</t>
         </is>
@@ -1980,19 +2081,19 @@
           <t>≤50 aceptable</t>
         </is>
       </c>
-      <c r="C8" s="28" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>≤20 dest. / ≤50 acept.</t>
         </is>
       </c>
-      <c r="D8" s="29" t="inlineStr">
+      <c r="D8" s="30" t="inlineStr">
         <is>
           <t>&gt;50 — requiere atención</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="30" t="inlineStr">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>ONE Score SEM</t>
         </is>
@@ -2002,19 +2103,19 @@
           <t>Por encima de la media (6,2)</t>
         </is>
       </c>
-      <c r="C9" s="28" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>&gt;6,2</t>
         </is>
       </c>
-      <c r="D9" s="29" t="inlineStr">
+      <c r="D9" s="30" t="inlineStr">
         <is>
           <t>≤6,2</t>
         </is>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="27" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>ONE Service CAM</t>
         </is>
@@ -2024,19 +2125,19 @@
           <t>≥8%</t>
         </is>
       </c>
-      <c r="C10" s="28" t="inlineStr">
+      <c r="C10" s="29" t="inlineStr">
         <is>
           <t>≥8%</t>
         </is>
       </c>
-      <c r="D10" s="29" t="inlineStr">
+      <c r="D10" s="30" t="inlineStr">
         <is>
           <t>5-8% regular / &lt;5% mejorar</t>
         </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="30" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>ONE Diferidos</t>
         </is>
@@ -2046,19 +2147,19 @@
           <t>≥8%</t>
         </is>
       </c>
-      <c r="C11" s="28" t="inlineStr">
+      <c r="C11" s="29" t="inlineStr">
         <is>
           <t>≥8%</t>
         </is>
       </c>
-      <c r="D11" s="29" t="inlineStr">
+      <c r="D11" s="30" t="inlineStr">
         <is>
           <t>5-8% regular / &lt;5% mejorar</t>
         </is>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="27" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>ONE Multimedia</t>
         </is>
@@ -2068,12 +2169,12 @@
           <t>≥5</t>
         </is>
       </c>
-      <c r="C12" s="28" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>≥5</t>
         </is>
       </c>
-      <c r="D12" s="29" t="inlineStr">
+      <c r="D12" s="30" t="inlineStr">
         <is>
           <t>3-5 regular / &lt;3 mejorar</t>
         </is>

--- a/informes/informe_seguimiento_dennis.xlsx
+++ b/informes/informe_seguimiento_dennis.xlsx
@@ -1687,7 +1687,7 @@
       </c>
       <c r="D5" s="22" t="inlineStr">
         <is>
-          <t>200 pts</t>
+          <t>220 pts</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="D11" s="22" t="inlineStr">
         <is>
-          <t>5,0</t>
+          <t>≥6</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D15" s="22" t="inlineStr">
         <is>
-          <t>≤50</t>
+          <t>&lt;20</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="D21" s="22" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>15%</t>
         </is>
       </c>
     </row>

--- a/informes/informe_seguimiento_dennis.xlsx
+++ b/informes/informe_seguimiento_dennis.xlsx
@@ -1626,7 +1626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1828,7 +1828,7 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>ONE KVPS</t>
+          <t>Cuadro CX</t>
         </is>
       </c>
     </row>
@@ -1857,81 +1857,131 @@
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="19" t="inlineStr">
         <is>
+          <t>CX total (/8)</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>≥7</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>ONE KVPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>Abr 2026</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>Objetivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
           <t>Score ONE</t>
         </is>
       </c>
-      <c r="B19" s="21" t="n">
+      <c r="B23" s="21" t="n">
         <v>6.1</v>
       </c>
-      <c r="C19" s="27" t="n">
+      <c r="C23" s="27" t="n">
         <v>5.3</v>
       </c>
-      <c r="D19" s="22" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>6,2</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="23" t="inlineStr">
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="23" t="inlineStr">
         <is>
           <t>Service CAM (%)</t>
         </is>
       </c>
-      <c r="B20" s="25" t="n">
+      <c r="B24" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="C20" s="25" t="n">
+      <c r="C24" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="22" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>Diferidos (%)</t>
         </is>
       </c>
-      <c r="B21" s="21" t="n">
+      <c r="B25" s="21" t="n">
         <v>32</v>
       </c>
-      <c r="C21" s="27" t="n">
+      <c r="C25" s="27" t="n">
         <v>30</v>
       </c>
-      <c r="D21" s="22" t="inlineStr">
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="23" t="inlineStr">
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="23" t="inlineStr">
         <is>
           <t>Multimedia</t>
         </is>
       </c>
-      <c r="B22" s="25" t="n">
+      <c r="B26" s="25" t="n">
         <v>7.4</v>
       </c>
-      <c r="C22" s="27" t="n">
+      <c r="C26" s="27" t="n">
         <v>6.8</v>
       </c>
-      <c r="D22" s="22" t="inlineStr">
+      <c r="D26" s="22" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A21:D21"/>
     <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/informes/informe_seguimiento_dennis.xlsx
+++ b/informes/informe_seguimiento_dennis.xlsx
@@ -11,7 +11,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mar 20261" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abr 2026" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolución" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Objetivos" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -93,7 +92,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -125,16 +124,6 @@
         <fgColor rgb="00FADBD8"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EAF7EE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDECEA"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -162,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -240,18 +229,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1986,254 +1963,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
-        <is>
-          <t>Objetivos y umbrales de referencia</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="17" t="inlineStr">
-        <is>
-          <t>Métrica</t>
-        </is>
-      </c>
-      <c r="B3" s="17" t="inlineStr">
-        <is>
-          <t>Referencia</t>
-        </is>
-      </c>
-      <c r="C3" s="17" t="inlineStr">
-        <is>
-          <t>Positivo si...</t>
-        </is>
-      </c>
-      <c r="D3" s="17" t="inlineStr">
-        <is>
-          <t>Mejorar si...</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="28" t="inlineStr">
-        <is>
-          <t>Desgaste total</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>&gt;200 pts</t>
-        </is>
-      </c>
-      <c r="C4" s="29" t="inlineStr">
-        <is>
-          <t>≥200 pts</t>
-        </is>
-      </c>
-      <c r="D4" s="30" t="inlineStr">
-        <is>
-          <t>&lt;200 pts — seguimiento prioritario</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="31" t="inlineStr">
-        <is>
-          <t>CAL1SEM</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>≥5,0</t>
-        </is>
-      </c>
-      <c r="C5" s="29" t="inlineStr">
-        <is>
-          <t>≥5,0</t>
-        </is>
-      </c>
-      <c r="D5" s="30" t="inlineStr">
-        <is>
-          <t>&lt;5,0</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="28" t="inlineStr">
-        <is>
-          <t>Full/Long Drive</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Media equipo: 11,1 ops</t>
-        </is>
-      </c>
-      <c r="C6" s="29" t="inlineStr">
-        <is>
-          <t>&gt;11,1 ops</t>
-        </is>
-      </c>
-      <c r="D6" s="30" t="inlineStr">
-        <is>
-          <t>≤11,1 ops</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="31" t="inlineStr">
-        <is>
-          <t>Fidelidad</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>Media equipo: 63,48%</t>
-        </is>
-      </c>
-      <c r="C7" s="29" t="inlineStr">
-        <is>
-          <t>≥63,48%</t>
-        </is>
-      </c>
-      <c r="D7" s="30" t="inlineStr">
-        <is>
-          <t>&lt;63,48%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="28" t="inlineStr">
-        <is>
-          <t>Horch Lauden (pos)</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>≤50 aceptable</t>
-        </is>
-      </c>
-      <c r="C8" s="29" t="inlineStr">
-        <is>
-          <t>≤20 dest. / ≤50 acept.</t>
-        </is>
-      </c>
-      <c r="D8" s="30" t="inlineStr">
-        <is>
-          <t>&gt;50 — requiere atención</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="31" t="inlineStr">
-        <is>
-          <t>ONE Score SEM</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>Por encima de la media (6,2)</t>
-        </is>
-      </c>
-      <c r="C9" s="29" t="inlineStr">
-        <is>
-          <t>&gt;6,2</t>
-        </is>
-      </c>
-      <c r="D9" s="30" t="inlineStr">
-        <is>
-          <t>≤6,2</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="28" t="inlineStr">
-        <is>
-          <t>ONE Service CAM</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>≥8%</t>
-        </is>
-      </c>
-      <c r="C10" s="29" t="inlineStr">
-        <is>
-          <t>≥8%</t>
-        </is>
-      </c>
-      <c r="D10" s="30" t="inlineStr">
-        <is>
-          <t>5-8% regular / &lt;5% mejorar</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="31" t="inlineStr">
-        <is>
-          <t>ONE Diferidos</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>≥8%</t>
-        </is>
-      </c>
-      <c r="C11" s="29" t="inlineStr">
-        <is>
-          <t>≥8%</t>
-        </is>
-      </c>
-      <c r="D11" s="30" t="inlineStr">
-        <is>
-          <t>5-8% regular / &lt;5% mejorar</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="28" t="inlineStr">
-        <is>
-          <t>ONE Multimedia</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>≥5</t>
-        </is>
-      </c>
-      <c r="C12" s="29" t="inlineStr">
-        <is>
-          <t>≥5</t>
-        </is>
-      </c>
-      <c r="D12" s="30" t="inlineStr">
-        <is>
-          <t>3-5 regular / &lt;3 mejorar</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/informes/informe_seguimiento_dennis.xlsx
+++ b/informes/informe_seguimiento_dennis.xlsx
@@ -1196,7 +1196,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Fecha: 06/05/2026</t>
+          <t>Fecha: 07/05/2026</t>
         </is>
       </c>
     </row>
@@ -1482,6 +1482,11 @@
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>Observaciones</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
         <is>
           <t>Grado de cumplimentación</t>
         </is>
@@ -1496,6 +1501,7 @@
       <c r="B44" s="13" t="inlineStr"/>
       <c r="C44" s="13" t="inlineStr"/>
       <c r="D44" s="13" t="inlineStr"/>
+      <c r="E44" s="13" t="inlineStr"/>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="14" t="inlineStr">
@@ -1506,6 +1512,7 @@
       <c r="B45" s="14" t="inlineStr"/>
       <c r="C45" s="14" t="inlineStr"/>
       <c r="D45" s="14" t="inlineStr"/>
+      <c r="E45" s="14" t="inlineStr"/>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="13" t="inlineStr">
@@ -1516,6 +1523,7 @@
       <c r="B46" s="13" t="inlineStr"/>
       <c r="C46" s="13" t="inlineStr"/>
       <c r="D46" s="13" t="inlineStr"/>
+      <c r="E46" s="13" t="inlineStr"/>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="14" t="inlineStr">
@@ -1526,6 +1534,7 @@
       <c r="B47" s="14" t="inlineStr"/>
       <c r="C47" s="14" t="inlineStr"/>
       <c r="D47" s="14" t="inlineStr"/>
+      <c r="E47" s="14" t="inlineStr"/>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="13" t="inlineStr">
@@ -1536,6 +1545,7 @@
       <c r="B48" s="13" t="inlineStr"/>
       <c r="C48" s="13" t="inlineStr"/>
       <c r="D48" s="13" t="inlineStr"/>
+      <c r="E48" s="13" t="inlineStr"/>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="14" t="inlineStr">
@@ -1546,6 +1556,7 @@
       <c r="B49" s="14" t="inlineStr"/>
       <c r="C49" s="14" t="inlineStr"/>
       <c r="D49" s="14" t="inlineStr"/>
+      <c r="E49" s="14" t="inlineStr"/>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="13" t="inlineStr">
@@ -1556,6 +1567,7 @@
       <c r="B50" s="13" t="inlineStr"/>
       <c r="C50" s="13" t="inlineStr"/>
       <c r="D50" s="13" t="inlineStr"/>
+      <c r="E50" s="13" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="33">

--- a/informes/informe_seguimiento_dennis.xlsx
+++ b/informes/informe_seguimiento_dennis.xlsx
@@ -1168,7 +1168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1371,23 +1371,40 @@
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>Sin datos registrados</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>8. ONE KVPS</t>
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>PUNTOS POSITIVOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Medidas de Servicio (EC28): 0,00% — 2/2 pts  |  Referencia: 0pts &gt;5% | 1pt ≤5% | 2pts ≤1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>Conectividad Posventa: 47,76% — 2/2 pts  |  Referencia: 0pts &lt;25% | 1pt ≥25% | 2pts ≥45%</t>
         </is>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>PUNTOS POSITIVOS</t>
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>PUNTOS A MEJORAR</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1416,7 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Instalación ONE: Asesor</t>
+          <t>Satisfacción General (CEM Q4): 4,69 — 1/2 pts  |  Referencia: 0pts &lt;4,60 | 1pt ≥4,60 | 2pts ≥4,80</t>
         </is>
       </c>
     </row>
@@ -1411,166 +1428,204 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
+          <t>Información Proceso (TRS): 62,50% — 0/2 pts  |  Referencia: 0pts &lt;80% | 1pt ≥80% | 2pts ≥90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>8. ONE KVPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>PUNTOS POSITIVOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Instalación ONE: Asesor</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
           <t>Diferidos Acum.: 30% (media equipo: 16%; bueno ≥8%) — en rango positivo</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="28" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>Multimedia Acum.: 6,8 (media equipo: 6,1; bueno ≥5) — en rango positivo</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="10" t="inlineStr">
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>PUNTOS A MEJORAR</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="28" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>Score SEM: 5,3 (media equipo: 6,2) — por debajo de la media</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="28" customHeight="1">
-      <c r="A40" s="8" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B40" s="9" t="inlineStr">
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
         <is>
           <t>Service CAM Acum.: 5% (media equipo: 8%; bueno ≥8%) — en rango regular</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="4" t="inlineStr">
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>9. Tareas pendientes</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="12" t="inlineStr">
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="12" t="inlineStr">
         <is>
           <t>Tarea</t>
         </is>
       </c>
-      <c r="B43" s="12" t="inlineStr">
+      <c r="B48" s="12" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="C43" s="12" t="inlineStr">
+      <c r="C48" s="12" t="inlineStr">
         <is>
           <t>Fecha límite</t>
         </is>
       </c>
-      <c r="D43" s="12" t="inlineStr">
+      <c r="D48" s="12" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
       </c>
-      <c r="E43" s="12" t="inlineStr">
+      <c r="E48" s="12" t="inlineStr">
         <is>
           <t>Grado de cumplimentación</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="13" t="inlineStr">
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="13" t="inlineStr">
         <is>
           <t>Utilizar el Laser de desgaste</t>
         </is>
       </c>
-      <c r="B44" s="13" t="inlineStr"/>
-      <c r="C44" s="13" t="inlineStr"/>
-      <c r="D44" s="13" t="inlineStr"/>
-      <c r="E44" s="13" t="inlineStr"/>
-    </row>
-    <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="14" t="inlineStr">
+      <c r="B49" s="13" t="inlineStr"/>
+      <c r="C49" s="13" t="inlineStr"/>
+      <c r="D49" s="13" t="inlineStr"/>
+      <c r="E49" s="13" t="inlineStr"/>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="14" t="inlineStr">
         <is>
           <t>Service cam</t>
         </is>
       </c>
-      <c r="B45" s="14" t="inlineStr"/>
-      <c r="C45" s="14" t="inlineStr"/>
-      <c r="D45" s="14" t="inlineStr"/>
-      <c r="E45" s="14" t="inlineStr"/>
-    </row>
-    <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="13" t="inlineStr">
+      <c r="B50" s="14" t="inlineStr"/>
+      <c r="C50" s="14" t="inlineStr"/>
+      <c r="D50" s="14" t="inlineStr"/>
+      <c r="E50" s="14" t="inlineStr"/>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="13" t="inlineStr">
         <is>
           <t>Escalar puesto en copa horch</t>
         </is>
       </c>
-      <c r="B46" s="13" t="inlineStr"/>
-      <c r="C46" s="13" t="inlineStr"/>
-      <c r="D46" s="13" t="inlineStr"/>
-      <c r="E46" s="13" t="inlineStr"/>
-    </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="14" t="inlineStr">
+      <c r="B51" s="13" t="inlineStr"/>
+      <c r="C51" s="13" t="inlineStr"/>
+      <c r="D51" s="13" t="inlineStr"/>
+      <c r="E51" s="13" t="inlineStr"/>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="14" t="inlineStr">
         <is>
           <t>Sigue igual con la progresión que llevas en desgaste</t>
         </is>
       </c>
-      <c r="B47" s="14" t="inlineStr"/>
-      <c r="C47" s="14" t="inlineStr"/>
-      <c r="D47" s="14" t="inlineStr"/>
-      <c r="E47" s="14" t="inlineStr"/>
-    </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="13" t="inlineStr">
+      <c r="B52" s="14" t="inlineStr"/>
+      <c r="C52" s="14" t="inlineStr"/>
+      <c r="D52" s="14" t="inlineStr"/>
+      <c r="E52" s="14" t="inlineStr"/>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="13" t="inlineStr">
         <is>
           <t>Pedir 5 estrellas y conectar</t>
         </is>
       </c>
-      <c r="B48" s="13" t="inlineStr"/>
-      <c r="C48" s="13" t="inlineStr"/>
-      <c r="D48" s="13" t="inlineStr"/>
-      <c r="E48" s="13" t="inlineStr"/>
-    </row>
-    <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="14" t="inlineStr">
+      <c r="B53" s="13" t="inlineStr"/>
+      <c r="C53" s="13" t="inlineStr"/>
+      <c r="D53" s="13" t="inlineStr"/>
+      <c r="E53" s="13" t="inlineStr"/>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="14" t="inlineStr">
         <is>
           <t>Full long drive</t>
         </is>
       </c>
-      <c r="B49" s="14" t="inlineStr"/>
-      <c r="C49" s="14" t="inlineStr"/>
-      <c r="D49" s="14" t="inlineStr"/>
-      <c r="E49" s="14" t="inlineStr"/>
-    </row>
-    <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="13" t="inlineStr">
+      <c r="B54" s="14" t="inlineStr"/>
+      <c r="C54" s="14" t="inlineStr"/>
+      <c r="D54" s="14" t="inlineStr"/>
+      <c r="E54" s="14" t="inlineStr"/>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="13" t="inlineStr">
         <is>
           <t>Health check</t>
         </is>
       </c>
-      <c r="B50" s="13" t="inlineStr"/>
-      <c r="C50" s="13" t="inlineStr"/>
-      <c r="D50" s="13" t="inlineStr"/>
-      <c r="E50" s="13" t="inlineStr"/>
+      <c r="B55" s="13" t="inlineStr"/>
+      <c r="C55" s="13" t="inlineStr"/>
+      <c r="D55" s="13" t="inlineStr"/>
+      <c r="E55" s="13" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="33">
+  <mergeCells count="38">
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="A27:F27"/>
@@ -1579,30 +1634,35 @@
     <mergeCell ref="A26:F26"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A47:F47"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="A23:F23"/>
+    <mergeCell ref="B42:F42"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A43:F43"/>
     <mergeCell ref="A38:F38"/>
+    <mergeCell ref="B44:F44"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="A31:F31"/>
-    <mergeCell ref="B37:F37"/>
     <mergeCell ref="A34:F34"/>
     <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A39:F39"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="A24:F24"/>
+    <mergeCell ref="B33:F33"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A6:F6"/>
+    <mergeCell ref="B45:F45"/>
     <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B41:F41"/>
     <mergeCell ref="B35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1852,10 +1912,8 @@
       <c r="B19" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="C19" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C19" s="26" t="n">
+        <v>5</v>
       </c>
       <c r="D19" s="22" t="inlineStr">
         <is>
